--- a/Table/Excel/Text_Character.xlsx
+++ b/Table/Excel/Text_Character.xlsx
@@ -1,100 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TokTak\Desktop\Local\Unity\LOTW\LOTW\Table\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FE3578BA-6C0A-41C7-B077-30B0305F0FC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BC28AAE4-C0F5-4994-AED3-CA100F7D45E4}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Text_Character" sheetId="1" r:id="rId1"/>
+    <sheet name="Text_Character" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
-  <si>
-    <t>DataId</t>
-  </si>
-  <si>
-    <t>Key</t>
-  </si>
-  <si>
-    <t>Ko</t>
-  </si>
-  <si>
-    <t>En</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>character.shopkeeper.name</t>
-  </si>
-  <si>
-    <t>상점 주인</t>
-  </si>
-  <si>
-    <t>Shopkeeper</t>
-  </si>
-  <si>
-    <t>character.player.name</t>
-  </si>
-  <si>
-    <t>플레이어</t>
-  </si>
-  <si>
-    <t>Player</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="2"/>
+      <color rgb="FF808080"/>
       <sz val="11"/>
-      <color rgb="FF808080"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -110,20 +59,22 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -143,25 +94,85 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{9CFF45FE-4F60-4E2C-84AB-AAC524FAC29D}" name="Text_Character" displayName="Text_Character" ref="B2:E5" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="B2:E5" xr:uid="{9CFF45FE-4F60-4E2C-84AB-AAC524FAC29D}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Text_Character" displayName="Text_Character" ref="B2:E6" headerRowCount="1" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B2:E6"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{C237DF1A-AB48-4EE4-B3E6-1C64EAA155E3}" name="DataId"/>
-    <tableColumn id="2" xr3:uid="{DFAFCD9F-706C-4EC4-87EF-D455F81601AE}" name="Key" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{8CC2C9C4-0478-46E7-8F6D-F3B3CFBFA5CB}" name="Ko" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{327A9499-36F4-4529-97D1-9784A253869B}" name="En" dataDxfId="1"/>
+    <tableColumn id="1" name="DataId"/>
+    <tableColumn id="2" name="Key" dataDxfId="3"/>
+    <tableColumn id="3" name="Ko" dataDxfId="2"/>
+    <tableColumn id="4" name="En" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -463,78 +474,125 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9C3557A-D248-42D5-B47F-AF136856A169}">
-  <dimension ref="B2:E5"/>
-  <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.125" customWidth="1"/>
-    <col min="2" max="2" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.75" style="1" bestFit="1" customWidth="1"/>
+    <col width="3.125" customWidth="1" style="3" min="1" max="1"/>
+    <col width="9.625" bestFit="1" customWidth="1" style="3" min="2" max="2"/>
+    <col width="26.25" bestFit="1" customWidth="1" style="1" min="3" max="3"/>
+    <col width="9.625" bestFit="1" customWidth="1" style="1" min="4" max="4"/>
+    <col width="11.75" bestFit="1" customWidth="1" style="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="2" ht="16.5" customHeight="1" s="3">
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>DataId</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>Key</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>Ko</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>En</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="16.5" customHeight="1" s="3">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="16.5" customHeight="1" s="3">
+      <c r="B4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>character.shopkeeper.name</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>상점 주인</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Shopkeeper</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="16.5" customHeight="1" s="3">
+      <c r="B5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>character.player.name</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>플레이어</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Player</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>character.mayor.name</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>촌장</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>